--- a/web/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/web/files/九龙-启德-天玺．海第2B期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,6 +132,12 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -209,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -278,6 +284,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2161,7 +2170,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -10600,7 +10609,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -10615,7 +10624,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -10942,12 +10951,12 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 1157呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>

--- a/web/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/web/files/九龙-启德-天玺．海第2B期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,12 +132,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -215,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -284,9 +278,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2170,23 +2161,19 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>47729200</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>41253</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2195,12 +2182,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2210,7 +2197,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10619,12 +10606,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -10951,12 +10938,12 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 1157呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$4773万
+$41,253/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>

--- a/web/files/九龙-启德-天玺．海第2B期.xlsx
+++ b/web/files/九龙-启德-天玺．海第2B期.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -10943,7 +10943,7 @@
           <t>B | 1157呎 (4+房)
 $4773万
 $41,253/呎
-(26年-09月-28日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
